--- a/1차 개발 설계서/부록/DB/컬럼 및 제약.xlsx
+++ b/1차 개발 설계서/부록/DB/컬럼 및 제약.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'컬럼'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'제약과인덱스'!$A$1:$C$68</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'제약과인덱스'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'서비스강제'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'서비스강제'!$A$1:$C$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'서비스강제'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7592,7 +7592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7620,90 +7620,107 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>동시 참여</t>
+          <t>초대 관리</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>group 잠금·활성 중복유일·정원10명</t>
+          <t>issuer_user_id 기록·group/초대 잠금</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>초대시각·모임별 차단·현재 계정 검증</t>
+          <t>모든 현재 member 권한·타인 초대 취소·참여 종료와 멱등 재시도 재검증</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>보관 고정</t>
+          <t>동시 참여</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>첫 기준 계산·고정 이후 변경 거부</t>
+          <t>group 잠금·활성 중복유일·정원10명</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>첫 공개 완료 시각·현재 권한·기한 경합</t>
+          <t>초대시각·모임별 차단·현재 계정 검증</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>파일 공개</t>
+          <t>보관 고정</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>위치 미검증 파생 ready 거부·task별media유일</t>
+          <t>첫 기준 계산·고정 이후 변경 거부</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>실파일 제거 검증·콘텐츠 검사·완료 트랜잭션</t>
+          <t>첫 공개 완료 시각·현재 권한·기한 경합</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>일괄 수정</t>
+          <t>파일 공개</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>대상별 버전 컬럼·정합 FK</t>
+          <t>위치 미검증 파생 ready 거부·task별media유일</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>검사 뒤 전 대상 재검증·전체 단일 커밋</t>
+          <t>실파일 제거 검증·콘텐츠 검사·완료 트랜잭션</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>일괄 수정</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>대상별 버전 컬럼·정합 FK</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>검사 뒤 전 대상 재검증·전체 단일 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>감사 이력 append-only·서버 역할 분리</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>OIDC/MFA·역할·사유·당사자 확인</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:C7"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
